--- a/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
+++ b/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,76 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +122,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +202,45 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -818,7 +961,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17R号</t>
+          <t>寿山村道17N号</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -837,7 +980,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2801</v>
+        <v>2755</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -850,10 +993,10 @@
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>182530000</v>
+        <v>194580000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>65166</v>
+        <v>70628</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -864,7 +1007,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17G号</t>
+          <t>寿山村道17P号</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -883,7 +1026,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2927</v>
+        <v>2733</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -896,10 +1039,10 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>228420000</v>
+        <v>150645000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>78039</v>
+        <v>55121</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -910,7 +1053,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17H号</t>
+          <t>寿山村道17Q号</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -929,11 +1072,11 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2908</v>
+        <v>2719</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -941,26 +1084,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H11" s="5" t="n">
+        <v>117089000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>43063</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17K号</t>
+          <t>寿山村道17R号</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -979,7 +1118,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2950</v>
+        <v>2801</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -992,10 +1131,10 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>124996500</v>
+        <v>182530000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>42372</v>
+        <v>65166</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1006,7 +1145,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>寿山村道17M号</t>
+          <t>寿山村道17G号</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1025,7 +1164,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2967</v>
+        <v>2927</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1038,10 +1177,10 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>133680000</v>
+        <v>228420000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>45056</v>
+        <v>78039</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1052,7 +1191,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11B号</t>
+          <t>寿山村道17H号</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1071,11 +1210,11 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3602</v>
+        <v>2908</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1083,22 +1222,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>295282000</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>81977</v>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11D号</t>
+          <t>寿山村道17J号</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1117,7 +1260,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3605</v>
+        <v>2897</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1130,10 +1273,10 @@
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>264766200</v>
+        <v>128800000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>73444</v>
+        <v>44460</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1144,7 +1287,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11E号</t>
+          <t>寿山村道17K号</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1163,7 +1306,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3606</v>
+        <v>2950</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1176,10 +1319,10 @@
         </is>
       </c>
       <c r="H16" s="5" t="n">
-        <v>262836500</v>
+        <v>124996500</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>72889</v>
+        <v>42372</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1190,7 +1333,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11F号</t>
+          <t>寿山村道17L号</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1209,7 +1352,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3567</v>
+        <v>2948</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1222,10 +1365,10 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>283500000</v>
+        <v>126979000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>79479</v>
+        <v>43073</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1236,7 +1379,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>寿山村道11G号</t>
+          <t>寿山村道17M号</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1255,7 +1398,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3601</v>
+        <v>2967</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1268,10 +1411,10 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>310128000</v>
+        <v>133680000</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>86123</v>
+        <v>45056</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1282,7 +1425,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19A号</t>
+          <t>寿山村道11A号</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1301,7 +1444,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3227</v>
+        <v>3553</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1314,10 +1457,10 @@
         </is>
       </c>
       <c r="H19" s="5" t="n">
-        <v>229898800</v>
+        <v>287800000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>71242</v>
+        <v>81002</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1328,7 +1471,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19B号</t>
+          <t>寿山村道11B号</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1347,7 +1490,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3238</v>
+        <v>3602</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1360,10 +1503,10 @@
         </is>
       </c>
       <c r="H20" s="5" t="n">
-        <v>240000000</v>
+        <v>295282000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>74120</v>
+        <v>81977</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1374,7 +1517,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>寿山村道19E号</t>
+          <t>寿山村道11C号</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1393,7 +1536,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3212</v>
+        <v>3601</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1406,10 +1549,10 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>262260000</v>
+        <v>180000000</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>81650</v>
+        <v>49986</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -1420,44 +1563,550 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>寿山村道11D号</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>3605</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>264766200</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>73444</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道11E号</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>3606</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>262836500</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>72889</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道11F号</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>3567</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>283500000</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>79479</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道11G号</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>3601</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>310128000</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>86123</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道19A号</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>3227</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>229898800</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>71242</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道19B号</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>3238</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>240000000</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>74120</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道19C号</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>3238</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>238108000</v>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>73536</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道19D号</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>3238</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>231278800</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>71426</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道19E号</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>3212</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>262260000</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>81650</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道17A号</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>2989</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>208000000</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>69588</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>寿山村道9号</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>4271</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>388000000</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>90845</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
           <t>寿山村道19F号</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>4212</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="5" t="n">
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n">
         <v>376888000</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="I33" s="5" t="n">
         <v>89480</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1476,331 +2125,459 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>总价</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>寿山村道15号</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>282800000</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>寿山村道17B号</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>187800000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>寿山村道17C号</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>180800000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>寿山村道17D号</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>192800000</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>寿山村道17E号</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>205000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>寿山村道17F号</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>211000000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>寿山村道17R号</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>182530000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>寿山村道17G号</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>228420000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>寿山村道17H号</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>在售</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>寿山村道17K号</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>124996500</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>寿山村道17M号</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>133680000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>寿山村道11B号</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>295282000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>寿山村道11D号</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>264766200</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>寿山村道11E号</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>262836500</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>寿山村道11F号</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>283500000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>寿山村道11G号</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>310128000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>寿山村道19A号</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>229898800</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>寿山村道19B号</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>240000000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>寿山村道19E号</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>262260000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>寿山村道19F号</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>376888000</v>
-      </c>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Shouson Peak - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>31 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>30 套</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>位置 1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>位置 2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>位置 3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>位置 4</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>位置 5</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>位置 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>第 1 行</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道9号
+4271呎 (4+房)
+(已售)
+$3.88亿
+$90,845/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道11A号
+3553呎 (4+房)
+(已售)
+$2.88亿
+$81,002/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道11B号
+3602呎 (4+房)
+(已售)
+$2.95亿
+$81,977/呎</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道11C号
+3601呎 (4+房)
+(已售)
+$1.80亿
+$49,986/呎</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道11D号
+3605呎 (4+房)
+(已售)
+$2.65亿
+$73,444/呎</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道11E号
+3606呎 (4+房)
+(已售)
+$2.63亿
+$72,889/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道11F号
+3567呎 (4+房)
+(已售)
+$2.83亿
+$79,479/呎</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道11G号
+3601呎 (4+房)
+(已售)
+$3.10亿
+$86,123/呎</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道15号
+4111呎 (4+房)
+(已售)
+$2.83亿
+$68,791/呎</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17A号
+2989呎 (4+房)
+(已售)
+$2.08亿
+$69,588/呎</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17B号
+2834呎 (4+房)
+(已售)
+$1.88亿
+$66,267/呎</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17C号
+2736呎 (4+房)
+(已售)
+$1.81亿
+$66,082/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>第 3 行</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17D号
+2893呎 (4+房)
+(已售)
+$1.93亿
+$66,644/呎</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17E号
+2953呎 (4+房)
+(已售)
+$2.05亿
+$69,421/呎</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17F号
+2927呎 (4+房)
+(已售)
+$2.11亿
+$72,087/呎</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17G号
+2927呎 (4+房)
+(已售)
+$2.28亿
+$78,039/呎</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>寿山村道17H号
+2908呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17J号
+2897呎 (4+房)
+(已售)
+$1.29亿
+$44,460/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>第 4 行</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17K号
+2950呎 (4+房)
+(已售)
+$1.25亿
+$42,372/呎</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17L号
+2948呎 (4+房)
+(已售)
+$1.27亿
+$43,073/呎</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17M号
+2967呎 (4+房)
+(已售)
+$1.34亿
+$45,056/呎</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17N号
+2755呎 (4+房)
+(已售)
+$1.95亿
+$70,628/呎</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17P号
+2733呎 (4+房)
+(已售)
+$1.51亿
+$55,121/呎</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17Q号
+2719呎 (4+房)
+(已售)
+$1.17亿
+$43,063/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>第 5 行</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道17R号
+2801呎 (4+房)
+(已售)
+$1.83亿
+$65,166/呎</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道19A号
+3227呎 (4+房)
+(已售)
+$2.30亿
+$71,242/呎</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道19B号
+3238呎 (4+房)
+(已售)
+$2.40亿
+$74,120/呎</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道19C号
+3238呎 (4+房)
+(已售)
+$2.38亿
+$73,536/呎</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道19D号
+3238呎 (4+房)
+(已售)
+$2.31亿
+$71,426/呎</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道19E号
+3212呎 (4+房)
+(已售)
+$2.62亿
+$81,650/呎</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>第 6 行</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>寿山村道19F号
+4212呎 (4+房)
+(已售)
+$3.77亿
+$89,480/呎</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr"/>
+      <c r="D11" s="18" t="inlineStr"/>
+      <c r="E11" s="18" t="inlineStr"/>
+      <c r="F11" s="18" t="inlineStr"/>
+      <c r="G11" s="18" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
+++ b/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
@@ -617,7 +617,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -713,7 +713,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-01-31</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -759,7 +759,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-07-03</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -805,7 +805,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-05-31</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2012-04-19</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2011-06-21</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -943,7 +943,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2012-12-05</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -989,7 +989,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-22</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-10-31</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-07-16</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-09</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-06-13</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2013-12-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2017-04-17</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2013-12-17</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-11-10</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2014-01-02</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2012-04-26</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2016-08-15</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2257,7 +2257,7 @@
         <is>
           <t>寿山村道9号
 4271呎 (4+房)
-(已售)
+(16年-08月)
 $3.88亿
 $90,845/呎</t>
         </is>
@@ -2266,7 +2266,7 @@
         <is>
           <t>寿山村道11A号
 3553呎 (4+房)
-(已售)
+(18年-07月)
 $2.88亿
 $81,002/呎</t>
         </is>
@@ -2275,7 +2275,7 @@
         <is>
           <t>寿山村道11B号
 3602呎 (4+房)
-(已售)
+(21年-06月)
 $2.95亿
 $81,977/呎</t>
         </is>
@@ -2284,7 +2284,7 @@
         <is>
           <t>寿山村道11C号
 3601呎 (4+房)
-(已售)
+(26年-02月)
 $1.80亿
 $49,986/呎</t>
         </is>
@@ -2293,7 +2293,7 @@
         <is>
           <t>寿山村道11D号
 3605呎 (4+房)
-(已售)
+(16年-06月)
 $2.65亿
 $73,444/呎</t>
         </is>
@@ -2302,7 +2302,7 @@
         <is>
           <t>寿山村道11E号
 3606呎 (4+房)
-(已售)
+(13年-12月)
 $2.63亿
 $72,889/呎</t>
         </is>
@@ -2318,7 +2318,7 @@
         <is>
           <t>寿山村道11F号
 3567呎 (4+房)
-(已售)
+(17年-04月)
 $2.83亿
 $79,479/呎</t>
         </is>
@@ -2327,7 +2327,7 @@
         <is>
           <t>寿山村道11G号
 3601呎 (4+房)
-(已售)
+(21年-06月)
 $3.10亿
 $86,123/呎</t>
         </is>
@@ -2336,7 +2336,7 @@
         <is>
           <t>寿山村道15号
 4111呎 (4+房)
-(已售)
+(11年-01月)
 $2.83亿
 $68,791/呎</t>
         </is>
@@ -2345,7 +2345,7 @@
         <is>
           <t>寿山村道17A号
 2989呎 (4+房)
-(已售)
+(12年-04月)
 $2.08亿
 $69,588/呎</t>
         </is>
@@ -2354,7 +2354,7 @@
         <is>
           <t>寿山村道17B号
 2834呎 (4+房)
-(已售)
+(11年-07月)
 $1.88亿
 $66,267/呎</t>
         </is>
@@ -2363,7 +2363,7 @@
         <is>
           <t>寿山村道17C号
 2736呎 (4+房)
-(已售)
+(11年-05月)
 $1.81亿
 $66,082/呎</t>
         </is>
@@ -2379,7 +2379,7 @@
         <is>
           <t>寿山村道17D号
 2893呎 (4+房)
-(已售)
+(12年-04月)
 $1.93亿
 $66,644/呎</t>
         </is>
@@ -2388,7 +2388,7 @@
         <is>
           <t>寿山村道17E号
 2953呎 (4+房)
-(已售)
+(11年-06月)
 $2.05亿
 $69,421/呎</t>
         </is>
@@ -2397,7 +2397,7 @@
         <is>
           <t>寿山村道17F号
 2927呎 (4+房)
-(已售)
+(12年-12月)
 $2.11亿
 $72,087/呎</t>
         </is>
@@ -2406,7 +2406,7 @@
         <is>
           <t>寿山村道17G号
 2927呎 (4+房)
-(已售)
+(16年-10月)
 $2.28亿
 $78,039/呎</t>
         </is>
@@ -2424,7 +2424,7 @@
         <is>
           <t>寿山村道17J号
 2897呎 (4+房)
-(已售)
+(25年-06月)
 $1.29亿
 $44,460/呎</t>
         </is>
@@ -2440,7 +2440,7 @@
         <is>
           <t>寿山村道17K号
 2950呎 (4+房)
-(已售)
+(25年-07月)
 $1.25亿
 $42,372/呎</t>
         </is>
@@ -2449,7 +2449,7 @@
         <is>
           <t>寿山村道17L号
 2948呎 (4+房)
-(已售)
+(25年-08月)
 $1.27亿
 $43,073/呎</t>
         </is>
@@ -2458,7 +2458,7 @@
         <is>
           <t>寿山村道17M号
 2967呎 (4+房)
-(已售)
+(25年-09月)
 $1.34亿
 $45,056/呎</t>
         </is>
@@ -2467,7 +2467,7 @@
         <is>
           <t>寿山村道17N号
 2755呎 (4+房)
-(已售)
+(21年-06月)
 $1.95亿
 $70,628/呎</t>
         </is>
@@ -2476,7 +2476,7 @@
         <is>
           <t>寿山村道17P号
 2733呎 (4+房)
-(已售)
+(26年-05月)
 $1.51亿
 $55,121/呎</t>
         </is>
@@ -2485,7 +2485,7 @@
         <is>
           <t>寿山村道17Q号
 2719呎 (4+房)
-(已售)
+(25年-08月)
 $1.17亿
 $43,063/呎</t>
         </is>
@@ -2501,7 +2501,7 @@
         <is>
           <t>寿山村道17R号
 2801呎 (4+房)
-(已售)
+(26年-06月)
 $1.83亿
 $65,166/呎</t>
         </is>
@@ -2510,7 +2510,7 @@
         <is>
           <t>寿山村道19A号
 3227呎 (4+房)
-(已售)
+(13年-12月)
 $2.30亿
 $71,242/呎</t>
         </is>
@@ -2519,7 +2519,7 @@
         <is>
           <t>寿山村道19B号
 3238呎 (4+房)
-(已售)
+(19年-03月)
 $2.40亿
 $74,120/呎</t>
         </is>
@@ -2528,7 +2528,7 @@
         <is>
           <t>寿山村道19C号
 3238呎 (4+房)
-(已售)
+(14年-11月)
 $2.38亿
 $73,536/呎</t>
         </is>
@@ -2537,7 +2537,7 @@
         <is>
           <t>寿山村道19D号
 3238呎 (4+房)
-(已售)
+(14年-01月)
 $2.31亿
 $71,426/呎</t>
         </is>
@@ -2546,7 +2546,7 @@
         <is>
           <t>寿山村道19E号
 3212呎 (4+房)
-(已售)
+(18年-05月)
 $2.62亿
 $81,650/呎</t>
         </is>
@@ -2562,7 +2562,7 @@
         <is>
           <t>寿山村道19F号
 4212呎 (4+房)
-(已售)
+(17年-05月)
 $3.77亿
 $89,480/呎</t>
         </is>

--- a/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
+++ b/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
@@ -190,49 +190,49 @@
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -618,7 +618,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
+++ b/files/港岛-寿臣山及浅水湾-Shouson Peak.xlsx
@@ -190,49 +190,49 @@
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -618,7 +618,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
